--- a/extra/report/No4_課題4テスト結果.xlsx
+++ b/extra/report/No4_課題4テスト結果.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52EEFED6-30F9-48C4-9058-CAF8438E74F2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FF58599-9B73-4D24-A1E9-39E0E1B8A722}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="19" activeTab="35" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="38" activeTab="43" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ケース1" sheetId="2" r:id="rId1"/>
@@ -45,27 +45,22 @@
     <sheet name="ケース12-2" sheetId="46" r:id="rId35"/>
     <sheet name="ケース13-1" sheetId="48" r:id="rId36"/>
     <sheet name="ケース13-2" sheetId="47" r:id="rId37"/>
-    <sheet name="ケース14-1" sheetId="49" r:id="rId38"/>
-    <sheet name="ケース14-2" sheetId="50" r:id="rId39"/>
-    <sheet name="ケース15-1" sheetId="51" r:id="rId40"/>
-    <sheet name="ケース15-2" sheetId="52" r:id="rId41"/>
-    <sheet name="ケース15-3" sheetId="55" r:id="rId42"/>
-    <sheet name="ケース15-4" sheetId="56" r:id="rId43"/>
-    <sheet name="ケース16" sheetId="57" r:id="rId44"/>
+    <sheet name="ケース14" sheetId="57" r:id="rId38"/>
+    <sheet name="ケース15-1" sheetId="49" r:id="rId39"/>
+    <sheet name="ケース15-2" sheetId="50" r:id="rId40"/>
+    <sheet name="ケース16-1" sheetId="51" r:id="rId41"/>
+    <sheet name="ケース16-2" sheetId="52" r:id="rId42"/>
+    <sheet name="ケース16-3" sheetId="55" r:id="rId43"/>
+    <sheet name="ケース16-4" sheetId="56" r:id="rId44"/>
     <sheet name="ケース17-1" sheetId="58" r:id="rId45"/>
     <sheet name="ケース17-2" sheetId="59" r:id="rId46"/>
-    <sheet name="ケース18-1" sheetId="60" r:id="rId47"/>
-    <sheet name="ケース18-2" sheetId="61" r:id="rId48"/>
-    <sheet name="ケース18-3" sheetId="62" r:id="rId49"/>
-    <sheet name="ケース18-4" sheetId="67" r:id="rId50"/>
-    <sheet name="ケース18-5" sheetId="63" r:id="rId51"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="51">
   <si>
     <t>テスト内容：料金検索画面を確認する。</t>
     <phoneticPr fontId="1"/>
@@ -696,32 +691,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>確認内容：T-CHARGEテーブルに、フォームに入力した以下のレコードが追加されていること。
-料金ID(charge_id)：※整数自動生成
-料金名(charge_name)：料金2 
-料金(amount)：2000
-開始日(start_date)：2025-02-01
-終了日(end_date)：2025-03-01
-登録日(created_at)：※登録した日時
-更新日(updated_at)：登録した時間</t>
-    <rPh sb="0" eb="4">
-      <t>カクニンナイヨウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>確認内容：T-CHARGEテーブルに、フォームに入力した以下のレコードが追加されていないこと。
-料金ID(charge_id)：※整数自動生成
-料金名(charge_name)：料金3
-料金(amount)：3000
-開始日(start_date)：2025-03-01
-終了日(end_date)：2025-04-01</t>
-    <rPh sb="0" eb="4">
-      <t>カクニンナイヨウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>テスト内容：テストケースNo.12とは異なる料金情報を、料金新規追加画面のテキストボックスに入力し、料金新規追加画面のキャンセルボタンを押下する。</t>
     <rPh sb="3" eb="5">
       <t>ナイヨウ</t>
@@ -743,13 +712,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>テスト内容：テストケースNo.12,13,14とは異なる料金情報を、料金編集画面のテキストボックスに入力し、保存ボタンを押してから、料金編集画面の削除ボタンを押下する。</t>
-    <rPh sb="3" eb="5">
-      <t>ナイヨウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>確認内容：「削除してもよろしいですか？」とポップアップが表示されること。</t>
     <rPh sb="0" eb="4">
       <t>カクニンナイヨウ</t>
@@ -799,16 +761,38 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>テスト内容：テストケースNo.12,13,15とは異なる料金情報を、料金編集画面のテキストボックスに入力し、保存ボタンを押してから、料金編集画面の削除ボタンを押下する。</t>
+    <rPh sb="3" eb="5">
+      <t>ナイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>確認内容：T-CHARGEテーブルに、フォームに入力した以下のレコードが削除されていること。
+料金ID(charge_id)：23
+料金名(charge_name)：料金2
+料金(amount)：2000
+開始日(start_date)：2025-02-01
+終了日(end_date)：2025-03-01</t>
+    <rPh sb="0" eb="4">
+      <t>カクニンナイヨウ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>サクジョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>確認内容：T-CHARGEテーブルに、フォームに入力した以下のレコードに編集されていること。
 ＜編集前＞
-料金ID(charge_id)：※整数自動生成
+料金ID(charge_id)：21
 料金名(charge_name)：料金1
 料金(amount)：1000
 開始日(start_date)：2025-01-01
 終了日(end_date)：2025-02-01
 更新日(updated_at)：登録した時間
 ＜変更後＞
-料金ID(charge_id)：※整数自動生成
+料金ID(charge_id)：21
 料金名(charge_name)：料金6
 料金(amount)：6000
 開始日(start_date)：2025-06-01
@@ -820,15 +804,8 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>テスト内容：データベースのT-CHARGEテーブルを確認する。</t>
-    <rPh sb="3" eb="5">
-      <t>ナイヨウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t xml:space="preserve">確認内容：T-CHARGEテーブルに、フォームに入力した以下のレコードが追加されていること。
-料金ID(charge_id)：※整数自動生成
+    <t xml:space="preserve">確認内容：T-CHARGEテーブルの料金ID21が、、フォームに入力した以下のレコードに変更されていないこと。
+料金ID(charge_id)：21
 料金名(charge_name)：料金4
 料金(amount)：4000
 開始日(start_date)：2025-04-01
@@ -837,67 +814,37 @@
     <rPh sb="0" eb="4">
       <t>カクニンナイヨウ</t>
     </rPh>
+    <rPh sb="18" eb="20">
+      <t>リョウキン</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ヘンコウ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>確認内容：T-CHARGEテーブルに、フォームに入力した以下のレコードが追加されていないこと。
-料金ID(charge_id)：※整数自動生成
-料金名(charge_name)：料金5
-料金(amount)：5000
-開始日(start_date)：2025-05-01
-終了日(end_date)：2025-06-01</t>
+料金ID(charge_id)：23
+料金名(charge_name)：料金3
+料金(amount)：3000
+開始日(start_date)：2025-03-01
+終了日(end_date)：2025-04-01</t>
     <rPh sb="0" eb="4">
       <t>カクニンナイヨウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>確認内容：テストケースNo.12で入力した情報が追加されていること。（料金2）</t>
+    <t>確認内容：T-CHARGEテーブルに、フォームに入力した以下のレコードが追加されていること。
+料金ID(charge_id)：23
+料金名(charge_name)：料金2 
+料金(amount)：2000
+開始日(start_date)：2025-02-01
+終了日(end_date)：2025-03-01
+登録日(created_at)：2025-08-19
+更新日(updated_at)：登録した時間</t>
     <rPh sb="0" eb="4">
       <t>カクニンナイヨウ</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>リョウキン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>確認内容：テストケースNo.13入力した情報が追加されていないこと。（料金3）</t>
-    <rPh sb="0" eb="4">
-      <t>カクニンナイヨウ</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>リョウキン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>確認内容：テストケースNo.14で入力した情報が追加されていること。（料金4）</t>
-    <rPh sb="0" eb="4">
-      <t>カクニンナイヨウ</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>リョウキン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>確認内容：テストケースNo.14で入力した情報が追加されていないこと。（料金5）</t>
-    <rPh sb="0" eb="4">
-      <t>カクニンナイヨウ</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>リョウキン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>確認内容：テストケースNo.15で編集した情報が保存されていること。（料金6）</t>
-    <rPh sb="0" eb="4">
-      <t>カクニンナイヨウ</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>リョウキン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -6935,118 +6882,25 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing38.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>582350</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>143709</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31CF40BB-B245-4CCD-985F-D8AF715F5D07}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="685800"/>
-          <a:ext cx="9497750" cy="5973009"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>582350</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>834</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DA3FC6B1-C2DB-4821-B643-D1354BA713DE}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="6886575"/>
-          <a:ext cx="9497750" cy="5973009"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>600075</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>161925</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>257175</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="正方形/長方形 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C9236988-6FB5-4C6C-947E-3F2C253ECAA2}"/>
+        <xdr:cNvPr id="3" name="正方形/長方形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94226C1B-36C8-47C2-8FC3-CF9F6C5E72F8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7054,8 +6908,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1971675" y="5562600"/>
-          <a:ext cx="933450" cy="447675"/>
+          <a:off x="381000" y="4019550"/>
+          <a:ext cx="9324975" cy="200025"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7094,66 +6948,10 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>341212</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>352427</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="5" name="直線矢印コネクタ 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6ECFB059-D957-44F5-B751-15D93A382C8E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="2398612" y="6010275"/>
-          <a:ext cx="11215" cy="885825"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="38100">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing39.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing38.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -7163,17 +6961,17 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>268128</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>76976</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>582350</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>143709</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D63EB55-8FA3-44D0-B3C5-04F5BA53534A}"/>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{190B4303-880C-4A10-909B-F8A71ABB958E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7189,8 +6987,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="1714500"/>
-          <a:ext cx="10231278" cy="5563376"/>
+          <a:off x="0" y="685800"/>
+          <a:ext cx="9497750" cy="5973009"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7199,25 +6997,69 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>582350</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>143709</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{825899B1-BEE0-43B5-88FA-DB4F1A1DE847}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="6858000"/>
+          <a:ext cx="9497750" cy="5973009"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>552450</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>552450</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="正方形/長方形 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56425F39-C916-4A5A-A0FA-EAA94DBC7EF9}"/>
+        <xdr:cNvPr id="4" name="正方形/長方形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C0CF50A-13B9-4475-85A0-E44EBB3336DD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7225,8 +7067,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="419100" y="4152900"/>
-          <a:ext cx="9315450" cy="247650"/>
+          <a:off x="1238250" y="3562350"/>
+          <a:ext cx="685800" cy="390525"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7265,30 +7107,86 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>649025</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="6" name="直線矢印コネクタ 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{001832A4-01D1-47F7-86D1-C60EFB5A6C81}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="1334825" y="3971925"/>
+          <a:ext cx="36777" cy="2905125"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing39.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>582350</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:row>74</xdr:row>
       <xdr:rowOff>143709</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3798A34A-E101-4E83-A325-DEFB6CF0448C}"/>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D39D232-CDB8-4D9C-BC8C-85A1E7D8EE7F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7304,7 +7202,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="685800"/>
+          <a:off x="0" y="6858000"/>
           <a:ext cx="9497750" cy="5973009"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -7314,25 +7212,69 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>582350</xdr:colOff>
+      <xdr:row>111</xdr:row>
+      <xdr:rowOff>19884</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DA3FC6B1-C2DB-4821-B643-D1354BA713DE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="13077825"/>
+          <a:ext cx="9497750" cy="5973009"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>9524</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>142876</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>571499</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>66676</xdr:rowOff>
+      <xdr:colOff>600075</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="正方形/長方形 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB36C141-4B90-424A-942F-F9CF0724FE11}"/>
+        <xdr:cNvPr id="4" name="正方形/長方形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C9236988-6FB5-4C6C-947E-3F2C253ECAA2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7340,8 +7282,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1381124" y="2886076"/>
-          <a:ext cx="561975" cy="266700"/>
+          <a:off x="1971675" y="11029950"/>
+          <a:ext cx="933450" cy="447675"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7380,11 +7322,62 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing40.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>332047</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>352428</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="5" name="直線矢印コネクタ 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6ECFB059-D957-44F5-B751-15D93A382C8E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="2389447" y="11477625"/>
+          <a:ext cx="20381" cy="1609725"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -7400,10 +7393,59 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CFD591C9-5A7E-4A20-98CB-1E195EC52D4F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="685800"/>
+          <a:ext cx="9497750" cy="5973009"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>582350</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>143709</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="図 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9346F59E-26C4-4E5E-9B89-0F0976538421}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3798A34A-E101-4E83-A325-DEFB6CF0448C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7429,113 +7471,25 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>582350</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>143709</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AAF17644-9885-4C6E-81CE-09A15269DFF9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="6858000"/>
-          <a:ext cx="9497750" cy="5973009"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>582350</xdr:colOff>
-      <xdr:row>110</xdr:row>
-      <xdr:rowOff>143709</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B6F2DEC8-44FF-407F-9DB5-7A9A1044AC89}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="13030200"/>
-          <a:ext cx="9497750" cy="5973009"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:colOff>9524</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>142876</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>657225</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:colOff>571499</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>66676</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="正方形/長方形 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{05C99550-843E-498A-9152-56579F8A36E6}"/>
+        <xdr:cNvPr id="3" name="正方形/長方形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB36C141-4B90-424A-942F-F9CF0724FE11}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7543,8 +7497,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1371600" y="4838700"/>
-          <a:ext cx="657225" cy="485775"/>
+          <a:off x="1381124" y="2886076"/>
+          <a:ext cx="561975" cy="266700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7583,25 +7537,74 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing40.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>268128</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>76976</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4C0BB885-40BF-406E-86E8-BF76A7E70CE2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="1714500"/>
+          <a:ext cx="10231278" cy="5563376"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>581025</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>590550</xdr:colOff>
-      <xdr:row>71</xdr:row>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="正方形/長方形 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7124C2D-8441-4191-BA3E-164C3C3F36F5}"/>
+        <xdr:cNvPr id="3" name="正方形/長方形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56425F39-C916-4A5A-A0FA-EAA94DBC7EF9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7609,8 +7612,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7439025" y="11706225"/>
-          <a:ext cx="695325" cy="495300"/>
+          <a:off x="419100" y="3800475"/>
+          <a:ext cx="9315450" cy="247650"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7649,25 +7652,162 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing41.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>582350</xdr:colOff>
+      <xdr:row>110</xdr:row>
+      <xdr:rowOff>143709</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="図 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92516795-F979-4125-89F7-FD7B68EFDDC4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="13030200"/>
+          <a:ext cx="9497750" cy="5973009"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>582350</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>143709</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="図 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F09D929-BEC5-47BD-958A-CE8FD1A8F47E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="6858000"/>
+          <a:ext cx="9497750" cy="5973009"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>582350</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>143709</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="図 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E45B41C2-CD00-40F0-8C98-F563FB70EE1C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="685800"/>
+          <a:ext cx="9497750" cy="5973009"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>342900</xdr:colOff>
-      <xdr:row>79</xdr:row>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>47626</xdr:colOff>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>161925</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>390526</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="正方形/長方形 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F6579B9-487A-4B43-88D7-3F052E032033}"/>
+        <xdr:cNvPr id="5" name="正方形/長方形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{05C99550-843E-498A-9152-56579F8A36E6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7675,8 +7815,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2400300" y="13601700"/>
-          <a:ext cx="4619625" cy="1514475"/>
+          <a:off x="1419226" y="4000500"/>
+          <a:ext cx="342900" cy="333375"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7717,216 +7857,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>295277</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>295277</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="8" name="直線矢印コネクタ 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35659687-876A-42DC-ABC4-2027D68C1532}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7839077" y="12211050"/>
-          <a:ext cx="0" cy="771525"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="38100">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing41.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>582350</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>143709</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{91299BF1-F1DA-43A7-8BA6-BC022E923BA1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="685800"/>
-          <a:ext cx="9497750" cy="5973009"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>582350</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>143709</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{695A4E31-2EA1-4205-8F85-166B828E645A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="6858000"/>
-          <a:ext cx="9497750" cy="5973009"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>582350</xdr:colOff>
-      <xdr:row>110</xdr:row>
-      <xdr:rowOff>143709</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F85CB637-D170-491E-8A6B-80F96369249B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="13030200"/>
-          <a:ext cx="9497750" cy="5973009"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>581025</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>581025</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>67</xdr:row>
       <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="正方形/長方形 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A04E0C1-B1BF-49C6-86CA-CF66E7B1A139}"/>
+        <xdr:cNvPr id="6" name="正方形/長方形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7124C2D-8441-4191-BA3E-164C3C3F36F5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7934,8 +7881,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7439025" y="5543550"/>
-          <a:ext cx="685800" cy="485775"/>
+          <a:off x="7439025" y="11020425"/>
+          <a:ext cx="695325" cy="495300"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7976,23 +7923,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>48</xdr:row>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>79</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>590550</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="正方形/長方形 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BCD51023-0B57-4BAF-9BD6-244D4C572FDC}"/>
+        <xdr:cNvPr id="7" name="正方形/長方形 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F6579B9-487A-4B43-88D7-3F052E032033}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8000,8 +7947,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5905500" y="8286750"/>
-          <a:ext cx="857250" cy="390525"/>
+          <a:off x="2400300" y="13601700"/>
+          <a:ext cx="4619625" cy="1514475"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8042,32 +7989,32 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>144802</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>200027</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>295277</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>295277</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="7" name="直線矢印コネクタ 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4C4A7A57-3BBE-45AC-A36E-C23BB1972B9A}"/>
+        <xdr:cNvPr id="8" name="直線矢印コネクタ 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35659687-876A-42DC-ABC4-2027D68C1532}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="6317002" y="8658225"/>
-          <a:ext cx="55225" cy="4362450"/>
+        <a:xfrm>
+          <a:off x="7839077" y="11525250"/>
+          <a:ext cx="0" cy="1504950"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -8096,62 +8043,6 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>208586</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>219077</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="9" name="直線矢印コネクタ 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4EA5A0EB-6699-4CC1-AF73-858136709B1A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="7752386" y="6038850"/>
-          <a:ext cx="10491" cy="828675"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="38100">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -8161,21 +8052,21 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>582350</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:row>74</xdr:row>
       <xdr:rowOff>143709</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3358F369-00A2-448C-AC26-0A5B900C4871}"/>
+        <xdr:cNvPr id="11" name="図 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3123F878-1821-46AB-8264-BCE63E9905BA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8191,7 +8082,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="685800"/>
+          <a:off x="0" y="6858000"/>
           <a:ext cx="9497750" cy="5973009"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -8205,21 +8096,21 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>582350</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>143709</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E0C43E1-2492-478E-8D67-61C9687BE516}"/>
+        <xdr:cNvPr id="10" name="図 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD3D186D-15D4-47F7-89E1-2FC8D862465F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8235,7 +8126,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="6858000"/>
+          <a:off x="0" y="685800"/>
           <a:ext cx="9497750" cy="5973009"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -8245,61 +8136,17 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>582350</xdr:colOff>
-      <xdr:row>110</xdr:row>
-      <xdr:rowOff>143709</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{36023040-1296-41A4-A4E2-6B22FE5E7D7E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="13030200"/>
-          <a:ext cx="9497750" cy="5973009"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>581025</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>561975</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -8307,7 +8154,7 @@
         <xdr:cNvPr id="5" name="正方形/長方形 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7CF54EEE-24F4-40C7-8528-C9EF43B7616B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A04E0C1-B1BF-49C6-86CA-CF66E7B1A139}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8315,8 +8162,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7439025" y="5553075"/>
-          <a:ext cx="666750" cy="457200"/>
+          <a:off x="7448550" y="4838700"/>
+          <a:ext cx="685800" cy="485775"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8357,23 +8204,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>257175</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
       <xdr:row>48</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>466725</xdr:colOff>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
       <xdr:row>50</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="6" name="正方形/長方形 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{88339DFC-367C-4838-9C45-CA0539B7A9BE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BCD51023-0B57-4BAF-9BD6-244D4C572FDC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8381,8 +8228,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5057775" y="8296275"/>
-          <a:ext cx="895350" cy="390525"/>
+          <a:off x="5905500" y="8286750"/>
+          <a:ext cx="857250" cy="390525"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8423,23 +8270,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>236558</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>247652</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>144802</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>200027</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
         <xdr:cNvPr id="7" name="直線矢印コネクタ 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE9F4ABF-30F0-44A9-AA25-6B583E8602A8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4C4A7A57-3BBE-45AC-A36E-C23BB1972B9A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8447,8 +8294,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="7780358" y="6019800"/>
-          <a:ext cx="11094" cy="876300"/>
+          <a:off x="6317002" y="8658225"/>
+          <a:ext cx="55225" cy="4362450"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -8479,32 +8326,32 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>9527</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>208946</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>228603</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
         <xdr:cNvPr id="9" name="直線矢印コネクタ 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1827257B-A01E-4B00-A524-89632317CBA8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4EA5A0EB-6699-4CC1-AF73-858136709B1A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5495927" y="8686800"/>
-          <a:ext cx="19048" cy="4324350"/>
+        <a:xfrm flipH="1">
+          <a:off x="7752746" y="5334000"/>
+          <a:ext cx="19657" cy="1552575"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -8533,6 +8380,50 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>582350</xdr:colOff>
+      <xdr:row>110</xdr:row>
+      <xdr:rowOff>143709</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="図 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3CE97EA5-44A8-4042-8B1A-30DB23D6D129}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="13030200"/>
+          <a:ext cx="9497750" cy="5973009"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -8542,21 +8433,21 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>668178</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>76976</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>582350</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>143709</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D55A5A8-723F-4E49-A3D8-3CAF76005253}"/>
+        <xdr:cNvPr id="11" name="図 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F0D5971-3F3F-4AB6-BA44-468DF7332E48}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8572,8 +8463,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="1543050"/>
-          <a:ext cx="10231278" cy="5563376"/>
+          <a:off x="0" y="6858000"/>
+          <a:ext cx="9497750" cy="5973009"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8582,11 +8473,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing44.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -8602,54 +8488,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AAA30CBE-BA54-48DA-AE8C-AF30CEA5BAEF}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="685800"/>
-          <a:ext cx="9497750" cy="5973009"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>582350</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>143709</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{825899B1-BEE0-43B5-88FA-DB4F1A1DE847}"/>
+        <xdr:cNvPr id="10" name="図 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D4582E5-00AB-425E-B504-9969C82B9AE4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8665,7 +8507,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="6858000"/>
+          <a:off x="0" y="685800"/>
           <a:ext cx="9497750" cy="5973009"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -8677,23 +8519,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>552450</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>552450</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>609600</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="正方形/長方形 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C0CF50A-13B9-4475-85A0-E44EBB3336DD}"/>
+        <xdr:cNvPr id="5" name="正方形/長方形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7CF54EEE-24F4-40C7-8528-C9EF43B7616B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8701,8 +8543,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1238250" y="3562350"/>
-          <a:ext cx="685800" cy="390525"/>
+          <a:off x="7467600" y="4857750"/>
+          <a:ext cx="666750" cy="457200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8743,216 +8585,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>649025</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>2</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="6" name="直線矢印コネクタ 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{001832A4-01D1-47F7-86D1-C60EFB5A6C81}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="1334825" y="3971925"/>
-          <a:ext cx="36777" cy="2905125"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="38100">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing45.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>582350</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>143709</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0F39F8E-FBD5-499F-9CB9-23E1C3936556}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="685800"/>
-          <a:ext cx="9497750" cy="5973009"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>582350</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>143709</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C322783-4876-4D04-BEA3-E7B3E73C62E2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="6858000"/>
-          <a:ext cx="9497750" cy="5973009"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>582350</xdr:colOff>
-      <xdr:row>110</xdr:row>
-      <xdr:rowOff>143709</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF5CE2E1-F94E-43F7-A099-FC8DC610A728}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="13030200"/>
-          <a:ext cx="9497750" cy="5973009"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>438150</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>647700</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>257175</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>466725</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="正方形/長方形 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC2DE265-09F7-4F6E-9C52-AA5084A7905A}"/>
+        <xdr:cNvPr id="6" name="正方形/長方形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{88339DFC-367C-4838-9C45-CA0539B7A9BE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8960,8 +8609,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2495550" y="8943975"/>
-          <a:ext cx="5695950" cy="2038350"/>
+          <a:off x="5057775" y="8296275"/>
+          <a:ext cx="895350" cy="390525"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9002,23 +8651,228 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>438150</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>647700</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:colOff>276225</xdr:colOff>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>276227</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="7" name="直線矢印コネクタ 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE9F4ABF-30F0-44A9-AA25-6B583E8602A8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="7820025" y="5324475"/>
+          <a:ext cx="2" cy="1543050"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>9527</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="9" name="直線矢印コネクタ 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1827257B-A01E-4B00-A524-89632317CBA8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5495927" y="8686800"/>
+          <a:ext cx="19048" cy="4324350"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>582350</xdr:colOff>
+      <xdr:row>110</xdr:row>
+      <xdr:rowOff>143709</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="図 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BFFA659E-FF62-4F16-9511-70F38073D64D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="13030200"/>
+          <a:ext cx="9497750" cy="5973009"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing44.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>668178</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>76976</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5E7062B-0795-4154-A60E-562DF311631F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="1543050"/>
+          <a:ext cx="10231278" cy="5563376"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>447675</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="正方形/長方形 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DBD5DC9B-2091-4C12-893D-E23162472EFF}"/>
+        <xdr:cNvPr id="5" name="正方形/長方形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8215B8C-FDB6-4D9D-B70F-83C3ACD93E85}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9026,8 +8880,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2495550" y="2771775"/>
-          <a:ext cx="5695950" cy="2038350"/>
+          <a:off x="447675" y="3838575"/>
+          <a:ext cx="9324975" cy="200025"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9066,25 +8920,162 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing45.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>582350</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>143709</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0F39F8E-FBD5-499F-9CB9-23E1C3936556}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="685800"/>
+          <a:ext cx="9497750" cy="5973009"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>582350</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>143709</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C322783-4876-4D04-BEA3-E7B3E73C62E2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="6858000"/>
+          <a:ext cx="9497750" cy="5973009"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>582350</xdr:colOff>
+      <xdr:row>110</xdr:row>
+      <xdr:rowOff>143709</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF5CE2E1-F94E-43F7-A099-FC8DC610A728}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="13030200"/>
+          <a:ext cx="9497750" cy="5973009"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
       <xdr:row>64</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>647700</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="正方形/長方形 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D53D087D-B6E2-4736-98E6-AEA12BEA9008}"/>
+        <xdr:cNvPr id="5" name="正方形/長方形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC2DE265-09F7-4F6E-9C52-AA5084A7905A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9092,8 +9083,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1390650" y="11020425"/>
-          <a:ext cx="628650" cy="485775"/>
+          <a:off x="2495550" y="8943975"/>
+          <a:ext cx="5695950" cy="2038350"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9134,23 +9125,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>666750</xdr:colOff>
-      <xdr:row>88</xdr:row>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>609600</xdr:colOff>
-      <xdr:row>92</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="8" name="正方形/長方形 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9335CA8-08D6-4A74-95A6-8CD34C631F88}"/>
+        <xdr:cNvPr id="6" name="正方形/長方形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DBD5DC9B-2091-4C12-893D-E23162472EFF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9158,8 +9149,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1352550" y="15097125"/>
-          <a:ext cx="6800850" cy="714375"/>
+          <a:off x="2495550" y="2771775"/>
+          <a:ext cx="5695950" cy="2038350"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9201,127 +9192,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>106823</xdr:colOff>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
       <xdr:row>67</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>152402</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="9" name="直線矢印コネクタ 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{81C7E167-4770-47AB-A422-62DEB661327C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="1478423" y="11525250"/>
-          <a:ext cx="45579" cy="3600450"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="38100">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing46.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>115728</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>76976</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7B550510-3EAA-457B-8BA4-E486728B0522}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="3257550"/>
-          <a:ext cx="10231278" cy="5563376"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>438149</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>333374</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="正方形/長方形 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0ACD445B-8007-4458-902E-2D909D41B16A}"/>
+        <xdr:cNvPr id="7" name="正方形/長方形 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D53D087D-B6E2-4736-98E6-AEA12BEA9008}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9329,8 +9215,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="438149" y="5353050"/>
-          <a:ext cx="9324975" cy="200025"/>
+          <a:off x="1390650" y="11020425"/>
+          <a:ext cx="628650" cy="485775"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9369,74 +9255,25 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing47.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>630078</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>76976</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{240E9466-2DD8-4D55-9D58-45D97C4094C3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="685800"/>
-          <a:ext cx="10231278" cy="5563376"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>666750</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>609600</xdr:colOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="正方形/長方形 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF1AC928-6E71-425F-A0AA-EAA236D5CB0A}"/>
+        <xdr:cNvPr id="8" name="正方形/長方形 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9335CA8-08D6-4A74-95A6-8CD34C631F88}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9444,8 +9281,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="419100" y="2962275"/>
-          <a:ext cx="9296400" cy="209550"/>
+          <a:off x="1352550" y="15097125"/>
+          <a:ext cx="6800850" cy="714375"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9484,10 +9321,66 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>106823</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>152402</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="9" name="直線矢印コネクタ 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{81C7E167-4770-47AB-A422-62DEB661327C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="1478423" y="11525250"/>
+          <a:ext cx="45579" cy="3600450"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing48.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing46.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -9497,17 +9390,17 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>630078</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>115728</xdr:colOff>
       <xdr:row>36</xdr:row>
       <xdr:rowOff>76976</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FFECB208-3B7E-4070-ADE8-42584428FB38}"/>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EFF2DDFC-4E25-4121-A403-3C290200EF52}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9523,7 +9416,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="685800"/>
+          <a:off x="0" y="3257550"/>
           <a:ext cx="10231278" cy="5563376"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -9533,74 +9426,25 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing49.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>630078</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>76976</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{378C0A3B-980A-45BB-8A04-69AE58B467C1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="685800"/>
-          <a:ext cx="10231278" cy="5563376"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>466724</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:colOff>438149</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>333374</xdr:colOff>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>114299</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="3" name="正方形/長方形 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DEF455A-C47F-465B-BF80-B799EB0BD9AD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0ACD445B-8007-4458-902E-2D909D41B16A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9608,8 +9452,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="466724" y="3152775"/>
-          <a:ext cx="9248775" cy="219075"/>
+          <a:off x="438149" y="5353050"/>
+          <a:ext cx="9324975" cy="200025"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9725,170 +9569,6 @@
         <a:xfrm>
           <a:off x="2533649" y="2790825"/>
           <a:ext cx="5572125" cy="447675"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="38100">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing50.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>630078</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>76976</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{721F233A-5C38-44A0-AE78-496359971D54}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="685800"/>
-          <a:ext cx="10231278" cy="5563376"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing51.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>630078</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>76976</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1DF0B442-1078-4EA2-BBDB-F736B7EB66EC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="685800"/>
-          <a:ext cx="10231278" cy="5563376"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>447674</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>76199</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="正方形/長方形 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8CF4BBF-ED30-46A5-A851-259EE86DE213}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="447674" y="2790825"/>
-          <a:ext cx="9229725" cy="228600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -11357,9 +11037,9 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:9" s="3" customFormat="1" ht="121.5" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:9" s="3" customFormat="1" ht="108" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -11384,12 +11064,12 @@
   <sheetData>
     <row r="2" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -11409,12 +11089,12 @@
   <sheetData>
     <row r="2" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="81" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="F3" s="4"/>
     </row>
@@ -11486,18 +11166,18 @@
 </file>
 
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1ABC6BC-BD7F-42A3-B034-57B464EE463D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17313B67-ABA5-4568-B49B-CE0DB2A1F640}">
   <dimension ref="A2:A3"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="2" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -11508,21 +11188,18 @@
 </file>
 
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{445E0E94-DD1D-4CB2-9254-DE5EA189EECD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1ABC6BC-BD7F-42A3-B034-57B464EE463D}">
   <dimension ref="A2:A3"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <cols>
-    <col min="1" max="1" width="76.75" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="2" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="94.5" x14ac:dyDescent="0.15">
-      <c r="A3" s="1" t="s">
-        <v>50</v>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A3" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -11556,41 +11233,43 @@
 </file>
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{445E0E94-DD1D-4CB2-9254-DE5EA189EECD}">
+  <dimension ref="A2:A3"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="76.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="108" x14ac:dyDescent="0.15">
+      <c r="A3" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EC397B7-546E-46F7-B7FF-67335AE17157}">
   <dimension ref="A2:A3"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="2" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6D01BAD-BE25-4339-9BD3-01BEFFF9BA9E}">
-  <dimension ref="A2:A3"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -11602,18 +11281,18 @@
 </file>
 
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E51D38E3-9E07-4379-9DFB-EDAD9AFF900E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6D01BAD-BE25-4339-9BD3-01BEFFF9BA9E}">
   <dimension ref="A2:A3"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="2" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -11625,21 +11304,18 @@
 </file>
 
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF208134-024D-420F-A157-1CF1A84C8463}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E51D38E3-9E07-4379-9DFB-EDAD9AFF900E}">
   <dimension ref="A2:A3"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <cols>
-    <col min="1" max="1" width="80.5" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="2" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="81" x14ac:dyDescent="0.15">
-      <c r="A3" s="1" t="s">
-        <v>51</v>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A3" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -11651,24 +11327,28 @@
 </file>
 
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17313B67-ABA5-4568-B49B-CE0DB2A1F640}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF208134-024D-420F-A157-1CF1A84C8463}">
   <dimension ref="A2:A3"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="80.5" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="2" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A3" t="s">
-        <v>45</v>
+    <row r="3" spans="1:1" ht="81" x14ac:dyDescent="0.15">
+      <c r="A3" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -11679,12 +11359,12 @@
   <sheetData>
     <row r="2" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -11704,84 +11384,19 @@
   <sheetData>
     <row r="2" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="216" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54F82E99-881A-41AA-A6BC-3A2C4662B4D3}">
-  <dimension ref="A2:A3"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C75AB6A-5BBC-46AA-867D-8917AAB23485}">
-  <dimension ref="A2:A3"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD027CA2-7251-40E8-9D9F-E883E1CDA152}">
-  <dimension ref="A2:A3"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -11805,50 +11420,6 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E143E7A9-6F20-4E08-BFBA-1B47CBD71891}">
-  <dimension ref="A2:A3"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{046070F8-AE1D-43B1-832B-E579A74E9A34}">
-  <dimension ref="A2:A3"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -11951,15 +11522,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100C424317A42AA8449A97AAE94730ED181" ma:contentTypeVersion="6" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="9df5c7ff725c9e365f8a8503f6029c6b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="dab87824-9c6b-4a08-9c96-9c9ea904f12c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="98e3d8fd3bbedc5b58bd9df00d6be37e" ns2:_="">
     <xsd:import namespace="dab87824-9c6b-4a08-9c96-9c9ea904f12c"/>
@@ -12117,6 +11679,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8048152-0CA9-47E5-A6CC-6D3980A2E781}">
   <ds:schemaRefs>
@@ -12127,14 +11698,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25A96F8A-B775-40FD-BBE8-4BBDAB58FCAE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFE06169-F6B9-4EE2-B032-3DCCE6AFCC5C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12150,4 +11713,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25A96F8A-B775-40FD-BBE8-4BBDAB58FCAE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/extra/report/No4_課題4テスト結果.xlsx
+++ b/extra/report/No4_課題4テスト結果.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FF58599-9B73-4D24-A1E9-39E0E1B8A722}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{120C0954-FB89-4BCB-9B6A-B866C752E4F4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="38" activeTab="43" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="30" activeTab="45" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ケース1" sheetId="2" r:id="rId1"/>
@@ -823,26 +823,26 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>確認内容：T-CHARGEテーブルに、フォームに入力した以下のレコードが追加されていないこと。
-料金ID(charge_id)：23
-料金名(charge_name)：料金3
-料金(amount)：3000
-開始日(start_date)：2025-03-01
-終了日(end_date)：2025-04-01</t>
-    <rPh sb="0" eb="4">
-      <t>カクニンナイヨウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>確認内容：T-CHARGEテーブルに、フォームに入力した以下のレコードが追加されていること。
-料金ID(charge_id)：23
+料金ID(charge_id)：27
 料金名(charge_name)：料金2 
 料金(amount)：2000
 開始日(start_date)：2025-02-01
 終了日(end_date)：2025-03-01
 登録日(created_at)：2025-08-19
 更新日(updated_at)：登録した時間</t>
+    <rPh sb="0" eb="4">
+      <t>カクニンナイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>確認内容：T-CHARGEテーブルに、フォームに入力した以下のレコードが追加されていないこと。
+料金ID(charge_id)：28
+料金名(charge_name)：料金3
+料金(amount)：3000
+開始日(start_date)：2025-03-01
+終了日(end_date)：2025-04-01</t>
     <rPh sb="0" eb="4">
       <t>カクニンナイヨウ</t>
     </rPh>
@@ -6523,10 +6523,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27A29F9E-960F-4663-8983-82A8E5C95175}"/>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3CFEC51D-9176-40CE-9BB2-CEA9E9874CDB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6542,7 +6542,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="2057400"/>
+          <a:off x="0" y="1885950"/>
           <a:ext cx="10231278" cy="5563376"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6618,6 +6618,50 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>629866</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>143709</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EC448471-E15F-46A1-96D7-F23F87EC73D3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="7715250"/>
+          <a:ext cx="8716591" cy="5973009"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -6714,13 +6758,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
+      <xdr:colOff>619126</xdr:colOff>
       <xdr:row>28</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>657225</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>142876</xdr:colOff>
       <xdr:row>30</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
@@ -6737,8 +6781,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1390650" y="4857750"/>
-          <a:ext cx="638175" cy="438150"/>
+          <a:off x="1990726" y="4857750"/>
+          <a:ext cx="895350" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6779,14 +6823,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>323850</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>361950</xdr:colOff>
       <xdr:row>30</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>342901</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>381001</xdr:colOff>
       <xdr:row>39</xdr:row>
       <xdr:rowOff>114301</xdr:rowOff>
     </xdr:to>
@@ -6803,7 +6847,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="1695450" y="5295900"/>
+          <a:off x="2419350" y="5295900"/>
           <a:ext cx="19051" cy="1504951"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
@@ -6853,10 +6897,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F962BAC3-7736-4DB1-8D28-01748D4A518E}"/>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CEC338B0-8A44-4989-AD5F-FF85918EC100}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6948,74 +6992,25 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing38.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>582350</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>639391</xdr:colOff>
+      <xdr:row>72</xdr:row>
       <xdr:rowOff>143709</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="図 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{190B4303-880C-4A10-909B-F8A71ABB958E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="685800"/>
-          <a:ext cx="9497750" cy="5973009"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>582350</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>143709</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{825899B1-BEE0-43B5-88FA-DB4F1A1DE847}"/>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8514B077-B61F-4507-ACE3-0F7E2E684C5E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7031,6 +7026,116 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
+          <a:off x="0" y="7372350"/>
+          <a:ext cx="8716591" cy="5973009"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing38.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>485775</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="図 7" descr="C:\Users\yamaguchi-ryoka\Pictures\Screenshots\スクリーンショット 2025-08-20 084510.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A47B48A-905F-4FF0-AF68-7D9E82870A76}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="685800"/>
+          <a:ext cx="8715375" cy="5972175"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>582350</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>143709</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{825899B1-BEE0-43B5-88FA-DB4F1A1DE847}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
           <a:off x="0" y="6858000"/>
           <a:ext cx="9497750" cy="5973009"/>
         </a:xfrm>
@@ -7044,13 +7149,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>552450</xdr:colOff>
+      <xdr:colOff>152400</xdr:colOff>
       <xdr:row>20</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>552450</xdr:colOff>
+      <xdr:colOff>152400</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
@@ -7067,7 +7172,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1238250" y="3562350"/>
+          <a:off x="838200" y="3562350"/>
           <a:ext cx="685800" cy="390525"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -7380,23 +7485,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>582350</xdr:colOff>
+      <xdr:colOff>486991</xdr:colOff>
       <xdr:row>38</xdr:row>
       <xdr:rowOff>143709</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="図 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CFD591C9-5A7E-4A20-98CB-1E195EC52D4F}"/>
+        <xdr:cNvPr id="8" name="図 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{29A36914-606A-4D9B-9614-0FC06126300D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7412,8 +7517,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="685800"/>
-          <a:ext cx="9497750" cy="5973009"/>
+          <a:off x="685800" y="685800"/>
+          <a:ext cx="8716591" cy="5973009"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7422,74 +7527,25 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>582350</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>143709</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3798A34A-E101-4E83-A325-DEFB6CF0448C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="685800"/>
-          <a:ext cx="9497750" cy="5973009"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>9524</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>142876</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>571499</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>66676</xdr:rowOff>
+      <xdr:colOff>295274</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>133349</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="正方形/長方形 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB36C141-4B90-424A-942F-F9CF0724FE11}"/>
+        <xdr:cNvPr id="9" name="正方形/長方形 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F678E388-99A9-46EF-B922-C5BDC1B8417E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7497,8 +7553,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1381124" y="2886076"/>
-          <a:ext cx="561975" cy="266700"/>
+          <a:off x="1666874" y="3505200"/>
+          <a:ext cx="523875" cy="447675"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7537,10 +7593,66 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>287192</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>323855</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="10" name="直線矢印コネクタ 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A30DFE1-CBF9-4BEF-8F7D-EB0950B43FFF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="1658792" y="3952875"/>
+          <a:ext cx="36663" cy="2895600"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing40.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -7550,17 +7662,17 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>268128</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>76976</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>582350</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>143709</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4C0BB885-40BF-406E-86E8-BF76A7E70CE2}"/>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3798A34A-E101-4E83-A325-DEFB6CF0448C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7576,8 +7688,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="1714500"/>
-          <a:ext cx="10231278" cy="5563376"/>
+          <a:off x="0" y="685800"/>
+          <a:ext cx="9497750" cy="5973009"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7588,23 +7700,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>419100</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>9524</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:rowOff>142876</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>571499</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>66676</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="3" name="正方形/長方形 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56425F39-C916-4A5A-A0FA-EAA94DBC7EF9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB36C141-4B90-424A-942F-F9CF0724FE11}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7612,8 +7724,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="419100" y="3800475"/>
-          <a:ext cx="9315450" cy="247650"/>
+          <a:off x="1381124" y="2886076"/>
+          <a:ext cx="561975" cy="266700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7655,27 +7767,27 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing40.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>582350</xdr:colOff>
-      <xdr:row>110</xdr:row>
-      <xdr:rowOff>143709</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>268128</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>76976</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="図 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92516795-F979-4125-89F7-FD7B68EFDDC4}"/>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{029C9FEF-0214-4175-961B-A9D58745DBA1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7691,8 +7803,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="13030200"/>
-          <a:ext cx="9497750" cy="5973009"/>
+          <a:off x="0" y="1885950"/>
+          <a:ext cx="10231278" cy="5563376"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7701,113 +7813,25 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>582350</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>143709</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="図 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F09D929-BEC5-47BD-958A-CE8FD1A8F47E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="6858000"/>
-          <a:ext cx="9497750" cy="5973009"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>582350</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>143709</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="図 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E45B41C2-CD00-40F0-8C98-F563FB70EE1C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="685800"/>
-          <a:ext cx="9497750" cy="5973009"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>47626</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>390526</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="正方形/長方形 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{05C99550-843E-498A-9152-56579F8A36E6}"/>
+        <xdr:cNvPr id="3" name="正方形/長方形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56425F39-C916-4A5A-A0FA-EAA94DBC7EF9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7815,8 +7839,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1419226" y="4000500"/>
-          <a:ext cx="342900" cy="333375"/>
+          <a:off x="419100" y="3800475"/>
+          <a:ext cx="9315450" cy="247650"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7855,25 +7879,206 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>125041</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>143709</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{25E7210A-FF94-406E-A8E7-9FF98F04A1A3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="7715250"/>
+          <a:ext cx="8716591" cy="5973009"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing41.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>486991</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>143709</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5006358B-6BD1-4B18-839B-FAB3CF7F54E5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="685800"/>
+          <a:ext cx="8716591" cy="5973009"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>582350</xdr:colOff>
+      <xdr:row>110</xdr:row>
+      <xdr:rowOff>143709</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="図 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92516795-F979-4125-89F7-FD7B68EFDDC4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="13030200"/>
+          <a:ext cx="9497750" cy="5973009"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>582350</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>143709</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="図 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F09D929-BEC5-47BD-958A-CE8FD1A8F47E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="6858000"/>
+          <a:ext cx="9497750" cy="5973009"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>581025</xdr:colOff>
-      <xdr:row>64</xdr:row>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>333376</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>676276</xdr:colOff>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>590550</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="正方形/長方形 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7124C2D-8441-4191-BA3E-164C3C3F36F5}"/>
+        <xdr:cNvPr id="5" name="正方形/長方形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{05C99550-843E-498A-9152-56579F8A36E6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7881,8 +8086,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7439025" y="11020425"/>
-          <a:ext cx="695325" cy="495300"/>
+          <a:off x="1019176" y="4000500"/>
+          <a:ext cx="342900" cy="333375"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7923,23 +8128,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>342900</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>161925</xdr:colOff>
-      <xdr:row>88</xdr:row>
+      <xdr:colOff>581025</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>67</xdr:row>
       <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="正方形/長方形 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F6579B9-487A-4B43-88D7-3F052E032033}"/>
+        <xdr:cNvPr id="6" name="正方形/長方形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7124C2D-8441-4191-BA3E-164C3C3F36F5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7947,8 +8152,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2400300" y="13601700"/>
-          <a:ext cx="4619625" cy="1514475"/>
+          <a:off x="7439025" y="11020425"/>
+          <a:ext cx="695325" cy="495300"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7989,172 +8194,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>295277</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>295277</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="8" name="直線矢印コネクタ 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35659687-876A-42DC-ABC4-2027D68C1532}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7839077" y="11525250"/>
-          <a:ext cx="0" cy="1504950"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="38100">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing42.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>582350</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>143709</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="図 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3123F878-1821-46AB-8264-BCE63E9905BA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="6858000"/>
-          <a:ext cx="9497750" cy="5973009"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>582350</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>143709</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="図 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD3D186D-15D4-47F7-89E1-2FC8D862465F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="685800"/>
-          <a:ext cx="9497750" cy="5973009"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>590550</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>590550</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="正方形/長方形 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A04E0C1-B1BF-49C6-86CA-CF66E7B1A139}"/>
+        <xdr:cNvPr id="7" name="正方形/長方形 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F6579B9-487A-4B43-88D7-3F052E032033}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8162,8 +8218,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7448550" y="4838700"/>
-          <a:ext cx="685800" cy="485775"/>
+          <a:off x="2400300" y="13601700"/>
+          <a:ext cx="4619625" cy="1514475"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8204,23 +8260,172 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>295277</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>295277</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="8" name="直線矢印コネクタ 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35659687-876A-42DC-ABC4-2027D68C1532}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7839077" y="11525250"/>
+          <a:ext cx="0" cy="1504950"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing42.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>582350</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>143709</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="図 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3123F878-1821-46AB-8264-BCE63E9905BA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="6858000"/>
+          <a:ext cx="9497750" cy="5973009"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>582350</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>143709</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="図 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD3D186D-15D4-47F7-89E1-2FC8D862465F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="685800"/>
+          <a:ext cx="9497750" cy="5973009"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>590550</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="正方形/長方形 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BCD51023-0B57-4BAF-9BD6-244D4C572FDC}"/>
+        <xdr:cNvPr id="5" name="正方形/長方形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A04E0C1-B1BF-49C6-86CA-CF66E7B1A139}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8228,8 +8433,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5905500" y="8286750"/>
-          <a:ext cx="857250" cy="390525"/>
+          <a:off x="7448550" y="4838700"/>
+          <a:ext cx="685800" cy="485775"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8270,272 +8475,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>144802</xdr:colOff>
+      <xdr:colOff>590550</xdr:colOff>
       <xdr:row>50</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>200027</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="7" name="直線矢印コネクタ 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4C4A7A57-3BBE-45AC-A36E-C23BB1972B9A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="6317002" y="8658225"/>
-          <a:ext cx="55225" cy="4362450"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="38100">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>208946</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>228603</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="9" name="直線矢印コネクタ 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4EA5A0EB-6699-4CC1-AF73-858136709B1A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="7752746" y="5334000"/>
-          <a:ext cx="19657" cy="1552575"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="38100">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>582350</xdr:colOff>
-      <xdr:row>110</xdr:row>
-      <xdr:rowOff>143709</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="図 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3CE97EA5-44A8-4042-8B1A-30DB23D6D129}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="13030200"/>
-          <a:ext cx="9497750" cy="5973009"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing43.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>582350</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>143709</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="図 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F0D5971-3F3F-4AB6-BA44-468DF7332E48}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="6858000"/>
-          <a:ext cx="9497750" cy="5973009"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>582350</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>143709</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="図 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D4582E5-00AB-425E-B504-9969C82B9AE4}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="685800"/>
-          <a:ext cx="9497750" cy="5973009"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>609600</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>590550</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="正方形/長方形 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7CF54EEE-24F4-40C7-8528-C9EF43B7616B}"/>
+        <xdr:cNvPr id="6" name="正方形/長方形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BCD51023-0B57-4BAF-9BD6-244D4C572FDC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8543,8 +8499,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7467600" y="4857750"/>
-          <a:ext cx="666750" cy="457200"/>
+          <a:off x="5905500" y="8286750"/>
+          <a:ext cx="857250" cy="390525"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8585,23 +8541,272 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>257175</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>466725</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>144802</xdr:colOff>
       <xdr:row>50</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>200027</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="7" name="直線矢印コネクタ 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4C4A7A57-3BBE-45AC-A36E-C23BB1972B9A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="6317002" y="8658225"/>
+          <a:ext cx="55225" cy="4362450"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>208946</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>228603</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="9" name="直線矢印コネクタ 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4EA5A0EB-6699-4CC1-AF73-858136709B1A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="7752746" y="5334000"/>
+          <a:ext cx="19657" cy="1552575"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>582350</xdr:colOff>
+      <xdr:row>110</xdr:row>
+      <xdr:rowOff>143709</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="図 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3CE97EA5-44A8-4042-8B1A-30DB23D6D129}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="13030200"/>
+          <a:ext cx="9497750" cy="5973009"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing43.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>582350</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>143709</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="図 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F0D5971-3F3F-4AB6-BA44-468DF7332E48}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="6858000"/>
+          <a:ext cx="9497750" cy="5973009"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>582350</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>143709</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="図 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D4582E5-00AB-425E-B504-9969C82B9AE4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="685800"/>
+          <a:ext cx="9497750" cy="5973009"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>609600</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="正方形/長方形 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{88339DFC-367C-4838-9C45-CA0539B7A9BE}"/>
+        <xdr:cNvPr id="5" name="正方形/長方形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7CF54EEE-24F4-40C7-8528-C9EF43B7616B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8609,8 +8814,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5057775" y="8296275"/>
-          <a:ext cx="895350" cy="390525"/>
+          <a:off x="7467600" y="4857750"/>
+          <a:ext cx="666750" cy="457200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8651,228 +8856,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>276225</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>276227</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="7" name="直線矢印コネクタ 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE9F4ABF-30F0-44A9-AA25-6B583E8602A8}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="7820025" y="5324475"/>
-          <a:ext cx="2" cy="1543050"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="38100">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>257175</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>9527</xdr:colOff>
+      <xdr:colOff>466725</xdr:colOff>
       <xdr:row>50</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="9" name="直線矢印コネクタ 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1827257B-A01E-4B00-A524-89632317CBA8}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5495927" y="8686800"/>
-          <a:ext cx="19048" cy="4324350"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="38100">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>582350</xdr:colOff>
-      <xdr:row>110</xdr:row>
-      <xdr:rowOff>143709</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="図 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BFFA659E-FF62-4F16-9511-70F38073D64D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="13030200"/>
-          <a:ext cx="9497750" cy="5973009"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing44.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>668178</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>76976</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5E7062B-0795-4154-A60E-562DF311631F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="1543050"/>
-          <a:ext cx="10231278" cy="5563376"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>447675</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>209550</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="正方形/長方形 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8215B8C-FDB6-4D9D-B70F-83C3ACD93E85}"/>
+        <xdr:cNvPr id="6" name="正方形/長方形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{88339DFC-367C-4838-9C45-CA0539B7A9BE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8880,8 +8880,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="447675" y="3838575"/>
-          <a:ext cx="9324975" cy="200025"/>
+          <a:off x="5057775" y="8296275"/>
+          <a:ext cx="895350" cy="390525"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8920,10 +8920,166 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>276225</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>276227</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="7" name="直線矢印コネクタ 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE9F4ABF-30F0-44A9-AA25-6B583E8602A8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="7820025" y="5324475"/>
+          <a:ext cx="2" cy="1543050"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>9527</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="9" name="直線矢印コネクタ 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1827257B-A01E-4B00-A524-89632317CBA8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5495927" y="8686800"/>
+          <a:ext cx="19048" cy="4324350"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>582350</xdr:colOff>
+      <xdr:row>110</xdr:row>
+      <xdr:rowOff>143709</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="図 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BFFA659E-FF62-4F16-9511-70F38073D64D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="13030200"/>
+          <a:ext cx="9497750" cy="5973009"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing44.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -8933,17 +9089,17 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>582350</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>143709</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>668178</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>76976</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0F39F8E-FBD5-499F-9CB9-23E1C3936556}"/>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5E7062B-0795-4154-A60E-562DF311631F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8959,8 +9115,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="685800"/>
-          <a:ext cx="9497750" cy="5973009"/>
+          <a:off x="0" y="1543050"/>
+          <a:ext cx="10231278" cy="5563376"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8969,113 +9125,25 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>582350</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>143709</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C322783-4876-4D04-BEA3-E7B3E73C62E2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="6858000"/>
-          <a:ext cx="9497750" cy="5973009"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>582350</xdr:colOff>
-      <xdr:row>110</xdr:row>
-      <xdr:rowOff>143709</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF5CE2E1-F94E-43F7-A099-FC8DC610A728}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="13030200"/>
-          <a:ext cx="9497750" cy="5973009"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>438150</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>647700</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:colOff>447675</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="5" name="正方形/長方形 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC2DE265-09F7-4F6E-9C52-AA5084A7905A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8215B8C-FDB6-4D9D-B70F-83C3ACD93E85}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9083,8 +9151,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2495550" y="8943975"/>
-          <a:ext cx="5695950" cy="2038350"/>
+          <a:off x="447675" y="3838575"/>
+          <a:ext cx="9324975" cy="200025"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9123,25 +9191,206 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>620450</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>143709</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{54EB1104-533B-4A1D-B3B5-D0AFFE2EFAD6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="7372350"/>
+          <a:ext cx="9497750" cy="5973009"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing45.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>582350</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>143709</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0F39F8E-FBD5-499F-9CB9-23E1C3936556}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="685800"/>
+          <a:ext cx="9497750" cy="5973009"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>582350</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>143709</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C322783-4876-4D04-BEA3-E7B3E73C62E2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="6858000"/>
+          <a:ext cx="9497750" cy="5973009"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>582350</xdr:colOff>
+      <xdr:row>110</xdr:row>
+      <xdr:rowOff>143709</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF5CE2E1-F94E-43F7-A099-FC8DC610A728}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="13030200"/>
+          <a:ext cx="9497750" cy="5973009"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>438150</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>52</xdr:row>
       <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>647700</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>64</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="正方形/長方形 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DBD5DC9B-2091-4C12-893D-E23162472EFF}"/>
+        <xdr:cNvPr id="5" name="正方形/長方形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC2DE265-09F7-4F6E-9C52-AA5084A7905A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9149,7 +9398,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2495550" y="2771775"/>
+          <a:off x="2495550" y="8943975"/>
           <a:ext cx="5695950" cy="2038350"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -9191,23 +9440,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>647700</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="正方形/長方形 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D53D087D-B6E2-4736-98E6-AEA12BEA9008}"/>
+        <xdr:cNvPr id="6" name="正方形/長方形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DBD5DC9B-2091-4C12-893D-E23162472EFF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9215,8 +9464,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1390650" y="11020425"/>
-          <a:ext cx="628650" cy="485775"/>
+          <a:off x="2495550" y="2771775"/>
+          <a:ext cx="5695950" cy="2038350"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9257,23 +9506,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>666750</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>609600</xdr:colOff>
-      <xdr:row>92</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="8" name="正方形/長方形 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9335CA8-08D6-4A74-95A6-8CD34C631F88}"/>
+        <xdr:cNvPr id="7" name="正方形/長方形 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D53D087D-B6E2-4736-98E6-AEA12BEA9008}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9281,8 +9530,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1352550" y="15097125"/>
-          <a:ext cx="6800850" cy="714375"/>
+          <a:off x="1390650" y="11020425"/>
+          <a:ext cx="628650" cy="485775"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9323,128 +9572,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>106823</xdr:colOff>
-      <xdr:row>67</xdr:row>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>666750</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>609600</xdr:colOff>
+      <xdr:row>92</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>152402</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="9" name="直線矢印コネクタ 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{81C7E167-4770-47AB-A422-62DEB661327C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="1478423" y="11525250"/>
-          <a:ext cx="45579" cy="3600450"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="38100">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing46.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>115728</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>76976</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EFF2DDFC-4E25-4121-A403-3C290200EF52}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="3257550"/>
-          <a:ext cx="10231278" cy="5563376"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>438149</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>333374</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="正方形/長方形 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0ACD445B-8007-4458-902E-2D909D41B16A}"/>
+        <xdr:cNvPr id="8" name="正方形/長方形 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9335CA8-08D6-4A74-95A6-8CD34C631F88}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9452,8 +9596,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="438149" y="5353050"/>
-          <a:ext cx="9324975" cy="200025"/>
+          <a:off x="1352550" y="15097125"/>
+          <a:ext cx="6800850" cy="714375"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9490,6 +9634,221 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>106823</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>152402</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="9" name="直線矢印コネクタ 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{81C7E167-4770-47AB-A422-62DEB661327C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="1478423" y="11525250"/>
+          <a:ext cx="45579" cy="3600450"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing46.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>115728</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>76976</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EFF2DDFC-4E25-4121-A403-3C290200EF52}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3257550"/>
+          <a:ext cx="10231278" cy="5563376"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>438149</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>333374</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="正方形/長方形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0ACD445B-8007-4458-902E-2D909D41B16A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="438149" y="5353050"/>
+          <a:ext cx="9324975" cy="200025"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>68000</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>143709</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E2FAE3B2-6216-440C-BF40-6E55449AD784}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="9086850"/>
+          <a:ext cx="9497750" cy="5973009"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -11039,7 +11398,7 @@
     </row>
     <row r="3" spans="1:9" s="3" customFormat="1" ht="108" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -11053,7 +11412,8 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -11094,7 +11454,7 @@
     </row>
     <row r="3" spans="1:6" ht="81" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F3" s="4"/>
     </row>
@@ -11522,6 +11882,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100C424317A42AA8449A97AAE94730ED181" ma:contentTypeVersion="6" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="9df5c7ff725c9e365f8a8503f6029c6b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="dab87824-9c6b-4a08-9c96-9c9ea904f12c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="98e3d8fd3bbedc5b58bd9df00d6be37e" ns2:_="">
     <xsd:import namespace="dab87824-9c6b-4a08-9c96-9c9ea904f12c"/>
@@ -11679,15 +12048,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8048152-0CA9-47E5-A6CC-6D3980A2E781}">
   <ds:schemaRefs>
@@ -11698,6 +12058,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25A96F8A-B775-40FD-BBE8-4BBDAB58FCAE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFE06169-F6B9-4EE2-B032-3DCCE6AFCC5C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11713,12 +12081,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25A96F8A-B775-40FD-BBE8-4BBDAB58FCAE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/extra/report/No4_課題4テスト結果.xlsx
+++ b/extra/report/No4_課題4テスト結果.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{120C0954-FB89-4BCB-9B6A-B866C752E4F4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B14988C5-E05F-46DC-8D6F-A837732ACCF8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="30" activeTab="45" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="30" activeTab="43" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ケース1" sheetId="2" r:id="rId1"/>
@@ -6523,10 +6523,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3CFEC51D-9176-40CE-9BB2-CEA9E9874CDB}"/>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{724002F3-284A-46FE-BB13-5BBA2BC09B97}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6556,14 +6556,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>428624</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>257174</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -6578,7 +6578,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="428624" y="4324350"/>
+          <a:off x="428624" y="5019675"/>
           <a:ext cx="9286875" cy="238125"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6618,50 +6618,6 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>629866</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>143709</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EC448471-E15F-46A1-96D7-F23F87EC73D3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="7715250"/>
-          <a:ext cx="8716591" cy="5973009"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -6897,10 +6853,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CEC338B0-8A44-4989-AD5F-FF85918EC100}"/>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{84157CEF-CA69-47AA-A80F-DD11F0FF7016}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6929,14 +6885,14 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>381000</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>257175</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:colOff>276225</xdr:colOff>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -6952,7 +6908,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="381000" y="4019550"/>
+          <a:off x="400050" y="4876800"/>
           <a:ext cx="9324975" cy="200025"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6992,50 +6948,6 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>639391</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>143709</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8514B077-B61F-4507-ACE3-0F7E2E684C5E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="7372350"/>
-          <a:ext cx="8716591" cy="5973009"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -7784,10 +7696,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{029C9FEF-0214-4175-961B-A9D58745DBA1}"/>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{368A2447-4C27-4DE0-A6C1-B244A046C0F7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7817,14 +7729,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -7839,7 +7751,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="419100" y="3800475"/>
+          <a:off x="419100" y="4838700"/>
           <a:ext cx="9315450" cy="247650"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -7879,50 +7791,6 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>125041</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>143709</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="図 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{25E7210A-FF94-406E-A8E7-9FF98F04A1A3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="7715250"/>
-          <a:ext cx="8716591" cy="5973009"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -9096,10 +8964,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5E7062B-0795-4154-A60E-562DF311631F}"/>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{76634866-0FE0-4B4A-8986-CDDE6CA523FB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9129,14 +8997,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>447675</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>209550</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -9151,7 +9019,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="447675" y="3838575"/>
+          <a:off x="447675" y="4619625"/>
           <a:ext cx="9324975" cy="200025"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -9191,50 +9059,6 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>620450</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>143709</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{54EB1104-533B-4A1D-B3B5-D0AFFE2EFAD6}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="7372350"/>
-          <a:ext cx="9497750" cy="5973009"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -9712,10 +9536,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EFF2DDFC-4E25-4121-A403-3C290200EF52}"/>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D5F89198-5776-47EE-91AA-E1E09D58E140}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9745,14 +9569,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>438149</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>333374</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -9767,7 +9591,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="438149" y="5353050"/>
+          <a:off x="438149" y="6143625"/>
           <a:ext cx="9324975" cy="200025"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -9805,50 +9629,6 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>68000</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>143709</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="図 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E2FAE3B2-6216-440C-BF40-6E55449AD784}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="9086850"/>
-          <a:ext cx="9497750" cy="5973009"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -11882,15 +11662,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100C424317A42AA8449A97AAE94730ED181" ma:contentTypeVersion="6" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="9df5c7ff725c9e365f8a8503f6029c6b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="dab87824-9c6b-4a08-9c96-9c9ea904f12c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="98e3d8fd3bbedc5b58bd9df00d6be37e" ns2:_="">
     <xsd:import namespace="dab87824-9c6b-4a08-9c96-9c9ea904f12c"/>
@@ -12048,6 +11819,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8048152-0CA9-47E5-A6CC-6D3980A2E781}">
   <ds:schemaRefs>
@@ -12058,14 +11838,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25A96F8A-B775-40FD-BBE8-4BBDAB58FCAE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFE06169-F6B9-4EE2-B032-3DCCE6AFCC5C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12081,4 +11853,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25A96F8A-B775-40FD-BBE8-4BBDAB58FCAE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>